--- a/data/trans_orig/POLIPATOLOGIA_5-Clase-trans_orig.xlsx
+++ b/data/trans_orig/POLIPATOLOGIA_5-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con cinco o más enfermedades crónicas en 2007</t>
+          <t>Población con cinco o más enfermedades crónicas en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6897</t>
+          <t>7308</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23091</t>
+          <t>22047</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8404</t>
+          <t>8354</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23580</t>
+          <t>24292</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18399</t>
+          <t>17966</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39874</t>
+          <t>39650</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,08%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>450685</t>
+          <t>451729</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>466879</t>
+          <t>466468</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>283100</t>
+          <t>282388</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>298276</t>
+          <t>298326</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>740583</t>
+          <t>740807</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>762058</t>
+          <t>762491</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,7%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3790</t>
+          <t>3812</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15060</t>
+          <t>16039</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7876</t>
+          <t>7347</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23915</t>
+          <t>23532</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14176</t>
+          <t>14013</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>34488</t>
+          <t>32860</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,45%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>351874</t>
+          <t>350895</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>363144</t>
+          <t>363122</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>347950</t>
+          <t>348333</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>363989</t>
+          <t>364518</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>704311</t>
+          <t>705939</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>724623</t>
+          <t>724786</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,1%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10308</t>
+          <t>10919</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27892</t>
+          <t>27548</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8336</t>
+          <t>7909</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24015</t>
+          <t>23294</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21564</t>
+          <t>21766</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>44323</t>
+          <t>44570</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,28%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>514497</t>
+          <t>514841</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>532081</t>
+          <t>531470</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>143767</t>
+          <t>144488</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>159446</t>
+          <t>159873</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,69%</t>
+          <t>86,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>665848</t>
+          <t>665601</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>688607</t>
+          <t>688405</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,94%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>42833</t>
+          <t>41938</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>70134</t>
+          <t>71413</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>32193</t>
+          <t>31584</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>57895</t>
+          <t>56631</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>79207</t>
+          <t>80183</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>119328</t>
+          <t>118845</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,09%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1168200</t>
+          <t>1166921</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1195501</t>
+          <t>1196396</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>656390</t>
+          <t>657654</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>682092</t>
+          <t>682701</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1833292</t>
+          <t>1833775</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1873413</t>
+          <t>1872437</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,89%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9896</t>
+          <t>10064</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>25641</t>
+          <t>24312</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>27876</t>
+          <t>27671</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>51330</t>
+          <t>54093</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>41635</t>
+          <t>42114</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>70904</t>
+          <t>70756</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,7%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>324914</t>
+          <t>326243</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>340659</t>
+          <t>340491</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>517422</t>
+          <t>514659</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>540876</t>
+          <t>541081</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>90,49%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>848403</t>
+          <t>848551</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>877672</t>
+          <t>877193</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,42%</t>
         </is>
       </c>
     </row>
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4587</t>
+          <t>4614</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>84190</t>
+          <t>84960</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>123892</t>
+          <t>125575</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>85231</t>
+          <t>85791</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>126179</t>
+          <t>122990</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>7,95%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>293614</t>
+          <t>293587</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1124868</t>
+          <t>1123185</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1164570</t>
+          <t>1163800</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,08%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1420781</t>
+          <t>1423970</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1461729</t>
+          <t>1461169</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>92,05%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,45%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>93569</t>
+          <t>92393</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>133017</t>
+          <t>134192</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>198097</t>
+          <t>200553</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>259381</t>
+          <t>260632</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>304440</t>
+          <t>305809</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>376632</t>
+          <t>374674</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,64%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3137173</t>
+          <t>3135998</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3176621</t>
+          <t>3177797</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3118743</t>
+          <t>3117492</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3180027</t>
+          <t>3177571</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6271682</t>
+          <t>6273640</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6343874</t>
+          <t>6342505</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,4%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con cinco o más enfermedades crónicas en 2012</t>
+          <t>Población con cinco o más enfermedades crónicas en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3373,7 +3373,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5309</t>
+          <t>5953</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7723</t>
+          <t>6823</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23918</t>
+          <t>24334</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8401</t>
+          <t>8345</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25748</t>
+          <t>24443</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3481,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>431902</t>
+          <t>431258</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>290536</t>
+          <t>290120</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>306731</t>
+          <t>307631</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>725917</t>
+          <t>727222</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>743264</t>
+          <t>743320</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,89%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3950</t>
+          <t>4026</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15281</t>
+          <t>15593</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9227</t>
+          <t>9934</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26839</t>
+          <t>27055</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16398</t>
+          <t>16033</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>38192</t>
+          <t>37180</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,91%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>403516</t>
+          <t>403204</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>414847</t>
+          <t>414771</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>311172</t>
+          <t>310956</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>328784</t>
+          <t>328077</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>718616</t>
+          <t>719628</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>740410</t>
+          <t>740775</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,88%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19836</t>
+          <t>20127</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>43414</t>
+          <t>44111</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9629</t>
+          <t>9912</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25096</t>
+          <t>25828</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>35067</t>
+          <t>35179</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>62114</t>
+          <t>62807</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,06%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>586001</t>
+          <t>585304</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>609579</t>
+          <t>609288</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>235033</t>
+          <t>234301</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>250500</t>
+          <t>250217</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>827430</t>
+          <t>826737</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>854477</t>
+          <t>854365</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>96,05%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>53723</t>
+          <t>53260</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>87675</t>
+          <t>88194</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>37681</t>
+          <t>37270</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>67030</t>
+          <t>66877</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>98934</t>
+          <t>98265</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>145738</t>
+          <t>145199</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,54%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1071334</t>
+          <t>1070815</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1105286</t>
+          <t>1105749</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>699627</t>
+          <t>699780</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>728976</t>
+          <t>729387</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>91,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1779929</t>
+          <t>1780468</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1826733</t>
+          <t>1827402</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,9%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12367</t>
+          <t>11411</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>29431</t>
+          <t>28866</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>85440</t>
+          <t>85210</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>124051</t>
+          <t>125832</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>102180</t>
+          <t>102874</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>145851</t>
+          <t>145752</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,46%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>481165</t>
+          <t>481730</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>498229</t>
+          <t>499185</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>637471</t>
+          <t>635690</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>676082</t>
+          <t>676312</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,71%</t>
+          <t>83,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>88,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1126267</t>
+          <t>1126366</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1169938</t>
+          <t>1169244</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>88,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>91,91%</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6302</t>
+          <t>7826</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>129147</t>
+          <t>125048</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>176116</t>
+          <t>174788</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>127915</t>
+          <t>130941</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>177190</t>
+          <t>176477</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,82%</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>260580</t>
+          <t>259056</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>933235</t>
+          <t>934563</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>980204</t>
+          <t>984303</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>84,12%</t>
+          <t>84,24%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>88,73%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1199043</t>
+          <t>1199756</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1248318</t>
+          <t>1245292</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>87,12%</t>
+          <t>87,18%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>90,49%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>107291</t>
+          <t>107838</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>154862</t>
+          <t>156277</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>314422</t>
+          <t>310719</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>390724</t>
+          <t>388443</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>439088</t>
+          <t>438876</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>530547</t>
+          <t>525988</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,54%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3267048</t>
+          <t>3265633</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3314619</t>
+          <t>3314072</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3159401</t>
+          <t>3161682</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3235703</t>
+          <t>3239406</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>89,06%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6441488</t>
+          <t>6446047</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6532947</t>
+          <t>6533159</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,71%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con cinco o más enfermedades crónicas en 2016</t>
+          <t>Población con cinco o más enfermedades crónicas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9382</t>
+          <t>9688</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26821</t>
+          <t>26959</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8602</t>
+          <t>9296</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24351</t>
+          <t>26161</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>22546</t>
+          <t>22685</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>46473</t>
+          <t>45789</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,9%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>402271</t>
+          <t>402133</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>419710</t>
+          <t>419404</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>322704</t>
+          <t>320894</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>338453</t>
+          <t>337759</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>729674</t>
+          <t>730358</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>753601</t>
+          <t>753462</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,08%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1918</t>
+          <t>1957</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12288</t>
+          <t>12552</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8783</t>
+          <t>8411</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27126</t>
+          <t>26891</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12584</t>
+          <t>12853</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>32804</t>
+          <t>33702</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>364939</t>
+          <t>364675</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>375309</t>
+          <t>375270</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>345147</t>
+          <t>345382</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>363490</t>
+          <t>363862</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>716696</t>
+          <t>715798</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>736916</t>
+          <t>736647</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,29%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7553</t>
+          <t>7658</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22614</t>
+          <t>22959</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15712</t>
+          <t>15553</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35691</t>
+          <t>35737</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>27354</t>
+          <t>28476</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>51825</t>
+          <t>53670</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,8%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>499300</t>
+          <t>498955</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>514361</t>
+          <t>514256</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>130432</t>
+          <t>130386</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>150411</t>
+          <t>150570</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>78,52%</t>
+          <t>78,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>636211</t>
+          <t>634366</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>660682</t>
+          <t>659560</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>95,86%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>32375</t>
+          <t>31407</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>57993</t>
+          <t>59240</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>43442</t>
+          <t>43446</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>72845</t>
+          <t>74208</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>82128</t>
+          <t>82851</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>122662</t>
+          <t>120959</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,12%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1091645</t>
+          <t>1090398</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1117263</t>
+          <t>1118231</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>753031</t>
+          <t>751668</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>782434</t>
+          <t>782430</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,7 +7195,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>91,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1852852</t>
+          <t>1854555</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1893386</t>
+          <t>1892663</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,81%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>28598</t>
+          <t>28387</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>52499</t>
+          <t>50565</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>81857</t>
+          <t>80727</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>121095</t>
+          <t>118488</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>118490</t>
+          <t>115334</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>165102</t>
+          <t>160354</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>11,8%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>568207</t>
+          <t>570141</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>592108</t>
+          <t>592319</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>617149</t>
+          <t>619756</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>656387</t>
+          <t>657517</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>83,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>89,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1193848</t>
+          <t>1198596</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1240460</t>
+          <t>1243616</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,85%</t>
+          <t>88,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>91,51%</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5700</t>
+          <t>6431</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>111137</t>
+          <t>112806</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>157761</t>
+          <t>157280</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>112887</t>
+          <t>113299</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>160054</t>
+          <t>157000</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,47%</t>
         </is>
       </c>
     </row>
@@ -7831,7 +7831,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>281445</t>
+          <t>280714</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>924264</t>
+          <t>924745</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>970888</t>
+          <t>969219</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,42%</t>
+          <t>85,46%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,73%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1209116</t>
+          <t>1212170</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1256283</t>
+          <t>1255871</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>91,72%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>98930</t>
+          <t>99332</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>139955</t>
+          <t>141149</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>307526</t>
+          <t>313142</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>383064</t>
+          <t>391427</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>419782</t>
+          <t>423128</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>508126</t>
+          <t>511200</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,39%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3245767</t>
+          <t>3244573</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3286792</t>
+          <t>3286390</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3148532</t>
+          <t>3140169</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3224070</t>
+          <t>3218454</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>88,92%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>91,13%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6409192</t>
+          <t>6406118</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6497536</t>
+          <t>6494190</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,88%</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con cinco o más enfermedades crónicas en 2023</t>
+          <t>Población con cinco o más enfermedades crónicas en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21071</t>
+          <t>21176</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>40172</t>
+          <t>39800</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>32361</t>
+          <t>32261</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>53608</t>
+          <t>51423</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>57715</t>
+          <t>57939</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>86197</t>
+          <t>85500</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>8,97%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>465040</t>
+          <t>465412</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>484141</t>
+          <t>484036</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>393859</t>
+          <t>396044</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>415106</t>
+          <t>415206</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,02%</t>
+          <t>88,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>866482</t>
+          <t>867179</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>894964</t>
+          <t>894740</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>91,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,92%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23465</t>
+          <t>23287</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>42421</t>
+          <t>41509</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>37161</t>
+          <t>36759</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>57314</t>
+          <t>57860</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>65743</t>
+          <t>66413</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>93553</t>
+          <t>93000</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,14%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>409792</t>
+          <t>410704</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>428748</t>
+          <t>428926</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>325266</t>
+          <t>324720</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>345419</t>
+          <t>345821</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,02%</t>
+          <t>84,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>741240</t>
+          <t>741793</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>769050</t>
+          <t>768380</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,79%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>92,04%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17094</t>
+          <t>16939</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>77837</t>
+          <t>80238</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>26903</t>
+          <t>26146</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>42681</t>
+          <t>42621</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>25,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>35846</t>
+          <t>36442</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>119710</t>
+          <t>118295</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,16%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>590427</t>
+          <t>588026</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>651170</t>
+          <t>651325</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>87,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>124230</t>
+          <t>124290</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>140008</t>
+          <t>140765</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>74,43%</t>
+          <t>74,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>83,88%</t>
+          <t>84,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>715465</t>
+          <t>716880</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>799329</t>
+          <t>798733</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,67%</t>
+          <t>85,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,64%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>95787</t>
+          <t>95123</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>131742</t>
+          <t>129976</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>110955</t>
+          <t>109988</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>625210</t>
+          <t>563018</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>63,92%</t>
+          <t>57,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>217270</t>
+          <t>218945</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>876078</t>
+          <t>924541</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>43,52%</t>
+          <t>45,93%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>903077</t>
+          <t>904843</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>939032</t>
+          <t>939696</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>87,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>90,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>352884</t>
+          <t>415076</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>867139</t>
+          <t>868106</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>42,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,66%</t>
+          <t>88,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1136834</t>
+          <t>1088371</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1795642</t>
+          <t>1793967</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>56,48%</t>
+          <t>54,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>89,12%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>37072</t>
+          <t>35825</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>60764</t>
+          <t>59949</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>140797</t>
+          <t>148838</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>224242</t>
+          <t>226428</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>198317</t>
+          <t>196257</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>270573</t>
+          <t>269943</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,51%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>414282</t>
+          <t>415097</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>437974</t>
+          <t>439221</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,21%</t>
+          <t>87,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>617093</t>
+          <t>614907</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>700538</t>
+          <t>692497</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>73,35%</t>
+          <t>73,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,27%</t>
+          <t>82,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1045808</t>
+          <t>1046438</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1118064</t>
+          <t>1120124</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>79,45%</t>
+          <t>79,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,93%</t>
+          <t>85,09%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2144</t>
+          <t>1904</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9346</t>
+          <t>8828</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>126543</t>
+          <t>127272</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>161063</t>
+          <t>161275</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>130279</t>
+          <t>131052</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>166871</t>
+          <t>166953</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,7 +10438,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>231161</t>
+          <t>231679</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>238363</t>
+          <t>238603</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>600308</t>
+          <t>600096</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>634828</t>
+          <t>634099</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>78,85%</t>
+          <t>78,82%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,38%</t>
+          <t>83,28%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>835007</t>
+          <t>834925</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>871599</t>
+          <t>870826</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10556,7 +10556,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,0%</t>
+          <t>86,92%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>212693</t>
+          <t>208211</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>305014</t>
+          <t>307055</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>572794</t>
+          <t>569078</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1293143</t>
+          <t>1282674</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>36,14%</t>
+          <t>35,85%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>824372</t>
+          <t>822691</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1599441</t>
+          <t>1665216</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>23,95%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3071046</t>
+          <t>3069005</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3163367</t>
+          <t>3167849</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2284615</t>
+          <t>2295084</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3004964</t>
+          <t>3008680</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>63,86%</t>
+          <t>64,15%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>84,09%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5354377</t>
+          <t>5288602</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6129446</t>
+          <t>6131127</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>77,0%</t>
+          <t>76,05%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>88,17%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/POLIPATOLOGIA_5-Clase-trans_orig.xlsx
+++ b/data/trans_orig/POLIPATOLOGIA_5-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7308</t>
+          <t>6743</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22047</t>
+          <t>21931</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8354</t>
+          <t>7544</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24292</t>
+          <t>23330</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17966</t>
+          <t>19098</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39650</t>
+          <t>39747</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,09%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>451729</t>
+          <t>451845</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>466468</t>
+          <t>467033</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>282388</t>
+          <t>283350</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>298326</t>
+          <t>299136</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>740807</t>
+          <t>740710</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>762491</t>
+          <t>761359</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,55%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3812</t>
+          <t>4369</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16039</t>
+          <t>15968</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7347</t>
+          <t>7686</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23532</t>
+          <t>23337</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,47 +1126,47 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
+          <t>2,07%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>6,28%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>22573</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>14622</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>33497</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>3,06%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
           <t>1,98%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>6,33%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>22573</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>14013</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>32860</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>3,06%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>1,9%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,53%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>350895</t>
+          <t>350966</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>363122</t>
+          <t>362565</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>348333</t>
+          <t>348528</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>364518</t>
+          <t>364179</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,47 +1239,47 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
+          <t>97,93%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>691</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>716226</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>705302</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>724177</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>96,94%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>95,47%</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
           <t>98,02%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>691</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>716226</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>705939</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>724786</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>96,94%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>95,55%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>98,1%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10919</t>
+          <t>10185</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27548</t>
+          <t>27006</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7909</t>
+          <t>8177</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23294</t>
+          <t>23984</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21766</t>
+          <t>22419</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>44570</t>
+          <t>44252</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,23%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>514841</t>
+          <t>515383</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>531470</t>
+          <t>532204</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>144488</t>
+          <t>143798</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>159873</t>
+          <t>159605</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>85,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>665601</t>
+          <t>665919</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>688405</t>
+          <t>687752</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,84%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>41938</t>
+          <t>42346</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>71413</t>
+          <t>70930</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>31584</t>
+          <t>31469</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>56631</t>
+          <t>56453</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>80183</t>
+          <t>79592</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>118845</t>
+          <t>117581</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,02%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1166921</t>
+          <t>1167404</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1196396</t>
+          <t>1195988</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>657654</t>
+          <t>657832</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>682701</t>
+          <t>682816</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1833775</t>
+          <t>1835039</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1872437</t>
+          <t>1873028</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,92%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10064</t>
+          <t>10261</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24312</t>
+          <t>25004</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>27671</t>
+          <t>26559</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>54093</t>
+          <t>52157</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>42114</t>
+          <t>41727</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>70756</t>
+          <t>69569</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,57%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>326243</t>
+          <t>325551</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>340491</t>
+          <t>340294</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>514659</t>
+          <t>516595</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>541081</t>
+          <t>542193</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>90,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>848551</t>
+          <t>849738</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>877193</t>
+          <t>877580</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,46%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4614</t>
+          <t>4599</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>84960</t>
+          <t>82777</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>125575</t>
+          <t>122908</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>85791</t>
+          <t>86499</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>122990</t>
+          <t>123787</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,0%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>293587</t>
+          <t>293602</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1123185</t>
+          <t>1125852</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1163800</t>
+          <t>1165983</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1423970</t>
+          <t>1423173</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1461169</t>
+          <t>1460461</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,41%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>92393</t>
+          <t>92989</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>134192</t>
+          <t>133511</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>200553</t>
+          <t>198795</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>260632</t>
+          <t>256965</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>305809</t>
+          <t>304714</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>374674</t>
+          <t>373814</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,62%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3135998</t>
+          <t>3136679</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3177797</t>
+          <t>3177201</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3117492</t>
+          <t>3121159</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3177571</t>
+          <t>3179329</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>94,12%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6273640</t>
+          <t>6274500</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6342505</t>
+          <t>6343600</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,42%</t>
         </is>
       </c>
     </row>
@@ -3373,7 +3373,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5953</t>
+          <t>5260</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6823</t>
+          <t>6940</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24334</t>
+          <t>22782</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8345</t>
+          <t>8065</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24443</t>
+          <t>24548</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3481,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>431258</t>
+          <t>431951</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>290120</t>
+          <t>291672</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>307631</t>
+          <t>307514</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>727222</t>
+          <t>727117</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>743320</t>
+          <t>743600</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,93%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4026</t>
+          <t>3977</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15593</t>
+          <t>15837</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9934</t>
+          <t>10009</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27055</t>
+          <t>26560</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16033</t>
+          <t>15497</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>37180</t>
+          <t>36365</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,81%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>403204</t>
+          <t>402960</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>414771</t>
+          <t>414820</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>310956</t>
+          <t>311451</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>328077</t>
+          <t>328002</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>719628</t>
+          <t>720443</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>740775</t>
+          <t>741311</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,95%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20127</t>
+          <t>20277</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>44111</t>
+          <t>43819</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9912</t>
+          <t>9604</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25828</t>
+          <t>26138</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>35179</t>
+          <t>34559</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>62807</t>
+          <t>62706</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,05%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>585304</t>
+          <t>585596</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>609288</t>
+          <t>609138</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>234301</t>
+          <t>233991</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>250217</t>
+          <t>250525</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>826737</t>
+          <t>826838</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>854365</t>
+          <t>854985</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,12%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>53260</t>
+          <t>55874</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>88194</t>
+          <t>91346</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>37270</t>
+          <t>39154</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>66877</t>
+          <t>68826</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>98265</t>
+          <t>99161</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>145199</t>
+          <t>144118</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,48%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1070815</t>
+          <t>1067663</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1105749</t>
+          <t>1103135</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>699780</t>
+          <t>697831</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>729387</t>
+          <t>727503</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1780468</t>
+          <t>1781549</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1827402</t>
+          <t>1826506</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,85%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11411</t>
+          <t>11825</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28866</t>
+          <t>29167</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>85210</t>
+          <t>86595</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>125832</t>
+          <t>122623</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>102874</t>
+          <t>103324</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>145752</t>
+          <t>146769</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,54%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>481730</t>
+          <t>481429</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>499185</t>
+          <t>498771</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>635690</t>
+          <t>638899</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>676312</t>
+          <t>674927</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,48%</t>
+          <t>83,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,81%</t>
+          <t>88,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1126366</t>
+          <t>1125349</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1169244</t>
+          <t>1168794</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,54%</t>
+          <t>88,46%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>91,88%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5088,7 +5088,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7826</t>
+          <t>6055</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>125048</t>
+          <t>128191</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>174788</t>
+          <t>175363</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>130941</t>
+          <t>127897</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>176477</t>
+          <t>174852</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,71%</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>259056</t>
+          <t>260827</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>934563</t>
+          <t>933988</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>984303</t>
+          <t>981160</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>84,19%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,73%</t>
+          <t>88,44%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1199756</t>
+          <t>1201381</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1245292</t>
+          <t>1248336</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>87,29%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>90,71%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>107838</t>
+          <t>106850</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>156277</t>
+          <t>154509</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>310719</t>
+          <t>315548</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>388443</t>
+          <t>388454</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>438876</t>
+          <t>434181</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>525988</t>
+          <t>522665</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,5%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3265633</t>
+          <t>3267401</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3314072</t>
+          <t>3315060</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3161682</t>
+          <t>3161671</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3239406</t>
+          <t>3234577</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5594,7 +5594,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>91,11%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6446047</t>
+          <t>6449370</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6533159</t>
+          <t>6537854</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,77%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9688</t>
+          <t>9290</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26959</t>
+          <t>26893</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9296</t>
+          <t>8737</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26161</t>
+          <t>25954</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>22685</t>
+          <t>22892</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>45789</t>
+          <t>47099</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,07%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>402133</t>
+          <t>402199</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>419404</t>
+          <t>419802</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>320894</t>
+          <t>321101</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>337759</t>
+          <t>338318</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>730358</t>
+          <t>729048</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>753462</t>
+          <t>753255</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,05%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1957</t>
+          <t>1933</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12552</t>
+          <t>12289</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8411</t>
+          <t>8400</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26891</t>
+          <t>26849</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12853</t>
+          <t>12838</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>33702</t>
+          <t>33547</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,48%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>364675</t>
+          <t>364938</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>375270</t>
+          <t>375294</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>345382</t>
+          <t>345424</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>363862</t>
+          <t>363873</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,7 +6509,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>715798</t>
+          <t>715953</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>736647</t>
+          <t>736662</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,7 +6544,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7658</t>
+          <t>7922</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22959</t>
+          <t>23437</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15553</t>
+          <t>15568</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35737</t>
+          <t>35239</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>28476</t>
+          <t>26480</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>53670</t>
+          <t>53040</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,71%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>498955</t>
+          <t>498477</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>514256</t>
+          <t>513992</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>130386</t>
+          <t>130884</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>150570</t>
+          <t>150555</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>78,49%</t>
+          <t>78,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>90,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>634366</t>
+          <t>634996</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>659560</t>
+          <t>661556</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>96,15%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31407</t>
+          <t>32495</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>59240</t>
+          <t>58382</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>43446</t>
+          <t>44070</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>74208</t>
+          <t>71908</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>82851</t>
+          <t>80311</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>120959</t>
+          <t>120662</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,11%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1090398</t>
+          <t>1091256</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1118231</t>
+          <t>1117143</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>751668</t>
+          <t>753968</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>782430</t>
+          <t>781806</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1854555</t>
+          <t>1854852</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1892663</t>
+          <t>1895203</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,93%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>28387</t>
+          <t>28472</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>50565</t>
+          <t>51601</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>80727</t>
+          <t>79181</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>118488</t>
+          <t>118041</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>115334</t>
+          <t>116321</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>160354</t>
+          <t>160536</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,81%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>570141</t>
+          <t>569105</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>592319</t>
+          <t>592234</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>619756</t>
+          <t>620203</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>657517</t>
+          <t>659063</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,95%</t>
+          <t>84,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,06%</t>
+          <t>89,27%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1198596</t>
+          <t>1198414</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1243616</t>
+          <t>1242629</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>88,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,44%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7723,7 +7723,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6431</t>
+          <t>5693</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>112806</t>
+          <t>112821</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>157280</t>
+          <t>156791</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7773,7 +7773,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>113299</t>
+          <t>113794</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>157000</t>
+          <t>161748</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,81%</t>
         </is>
       </c>
     </row>
@@ -7831,7 +7831,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>280714</t>
+          <t>281452</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>924745</t>
+          <t>925234</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>969219</t>
+          <t>969204</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,7 +7881,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
+          <t>85,51%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1212170</t>
+          <t>1207422</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1255871</t>
+          <t>1255376</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>88,19%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>91,69%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>99332</t>
+          <t>100731</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>141149</t>
+          <t>143874</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>313142</t>
+          <t>308726</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>391427</t>
+          <t>386353</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>423128</t>
+          <t>422214</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>511200</t>
+          <t>508456</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,35%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3244573</t>
+          <t>3241848</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3286390</t>
+          <t>3284991</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3140169</t>
+          <t>3145243</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3218454</t>
+          <t>3222870</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>89,06%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6406118</t>
+          <t>6408862</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6494190</t>
+          <t>6495104</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,65%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,9%</t>
         </is>
       </c>
     </row>
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>29797</t>
+          <t>33130</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21176</t>
+          <t>24760</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>39800</t>
+          <t>44996</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>40979</t>
+          <t>44982</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>32261</t>
+          <t>35508</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>51423</t>
+          <t>57661</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>70777</t>
+          <t>78112</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>57939</t>
+          <t>65324</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>85500</t>
+          <t>95002</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,14%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>475415</t>
+          <t>517488</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>465412</t>
+          <t>505622</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>484036</t>
+          <t>525858</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>406488</t>
+          <t>443429</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>396044</t>
+          <t>430750</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>415206</t>
+          <t>452903</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>90,79%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,51%</t>
+          <t>88,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>881902</t>
+          <t>960917</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>867179</t>
+          <t>944027</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>894740</t>
+          <t>973705</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,03%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>93,71%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,32 +8976,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>31840</t>
+          <t>33639</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23287</t>
+          <t>24764</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>41509</t>
+          <t>44528</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>46721</t>
+          <t>51854</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>36759</t>
+          <t>42504</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>57860</t>
+          <t>64116</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>78562</t>
+          <t>85494</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>66413</t>
+          <t>71281</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>93000</t>
+          <t>102879</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,35%</t>
         </is>
       </c>
     </row>
@@ -9089,32 +9089,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>420373</t>
+          <t>449573</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>410704</t>
+          <t>438684</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>428926</t>
+          <t>458448</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>90,78%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>335859</t>
+          <t>371289</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>324720</t>
+          <t>359027</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>345821</t>
+          <t>380639</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>87,79%</t>
+          <t>87,75%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,88%</t>
+          <t>84,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>89,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>756231</t>
+          <t>820861</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>741793</t>
+          <t>803476</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>768380</t>
+          <t>835074</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>92,14%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>46210</t>
+          <t>50209</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16939</t>
+          <t>38626</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>80238</t>
+          <t>63177</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>33998</t>
+          <t>37446</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>26146</t>
+          <t>29196</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>42621</t>
+          <t>46531</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>80208</t>
+          <t>87656</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>36442</t>
+          <t>72714</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>118295</t>
+          <t>103642</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>15,72%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>622054</t>
+          <t>421403</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>588026</t>
+          <t>408435</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>651325</t>
+          <t>432986</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>89,35%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,99%</t>
+          <t>86,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>132913</t>
+          <t>150051</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>124290</t>
+          <t>140966</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>140765</t>
+          <t>158301</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>79,63%</t>
+          <t>80,03%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>74,46%</t>
+          <t>75,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,34%</t>
+          <t>84,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>754967</t>
+          <t>571453</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>716880</t>
+          <t>555467</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>798733</t>
+          <t>586395</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>86,7%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,84%</t>
+          <t>84,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>88,97%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>111030</t>
+          <t>117379</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>95123</t>
+          <t>100642</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>129976</t>
+          <t>137538</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>297180</t>
+          <t>102740</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>109988</t>
+          <t>88421</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>563018</t>
+          <t>119262</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>57,56%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>408209</t>
+          <t>220119</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>218945</t>
+          <t>196949</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>924541</t>
+          <t>246640</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>45,93%</t>
+          <t>12,38%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>923789</t>
+          <t>1014464</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>904843</t>
+          <t>994305</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>939696</t>
+          <t>1031201</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>89,63%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,44%</t>
+          <t>87,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,81%</t>
+          <t>91,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>680914</t>
+          <t>758471</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>415076</t>
+          <t>741949</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>868106</t>
+          <t>772790</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>69,62%</t>
+          <t>88,07%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>42,44%</t>
+          <t>86,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>89,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1604703</t>
+          <t>1772935</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1088371</t>
+          <t>1746414</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1793967</t>
+          <t>1796105</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>79,72%</t>
+          <t>88,96%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>54,07%</t>
+          <t>87,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>90,12%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>47005</t>
+          <t>49579</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>35825</t>
+          <t>38430</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>59949</t>
+          <t>62930</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>193991</t>
+          <t>207250</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>148838</t>
+          <t>188520</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>226428</t>
+          <t>227515</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>240996</t>
+          <t>256830</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>196257</t>
+          <t>235158</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>269943</t>
+          <t>282056</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,16%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>428041</t>
+          <t>518385</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>415097</t>
+          <t>505034</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>439221</t>
+          <t>529534</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>91,27%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,38%</t>
+          <t>88,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>647344</t>
+          <t>623600</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>614907</t>
+          <t>603335</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>692497</t>
+          <t>642330</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>76,94%</t>
+          <t>75,06%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>73,09%</t>
+          <t>72,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>82,31%</t>
+          <t>77,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1075385</t>
+          <t>1141984</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1046438</t>
+          <t>1116758</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1120124</t>
+          <t>1163656</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>81,69%</t>
+          <t>81,64%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>79,49%</t>
+          <t>79,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,09%</t>
+          <t>83,19%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,32 +10348,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4409</t>
+          <t>6004</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1904</t>
+          <t>2584</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8828</t>
+          <t>12552</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>143271</t>
+          <t>154761</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>127272</t>
+          <t>138203</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>161275</t>
+          <t>173710</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,22 +10418,22 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>147680</t>
+          <t>160765</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>131052</t>
+          <t>141410</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>166953</t>
+          <t>182493</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
@@ -10443,7 +10443,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,87%</t>
         </is>
       </c>
     </row>
@@ -10461,32 +10461,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>236098</t>
+          <t>231224</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>231679</t>
+          <t>224676</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>238603</t>
+          <t>234644</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>618100</t>
+          <t>689520</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>600096</t>
+          <t>670571</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>634099</t>
+          <t>706078</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>81,18%</t>
+          <t>81,67%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>78,82%</t>
+          <t>79,43%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,28%</t>
+          <t>83,63%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,27 +10531,27 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>854198</t>
+          <t>920744</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>834925</t>
+          <t>899016</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>870826</t>
+          <t>940099</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>85,26%</t>
+          <t>85,14%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>83,34%</t>
+          <t>83,13%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>270291</t>
+          <t>289942</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>208211</t>
+          <t>259501</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>307055</t>
+          <t>321721</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>756140</t>
+          <t>599033</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>569078</t>
+          <t>563125</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1282674</t>
+          <t>635478</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1026432</t>
+          <t>888975</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>822691</t>
+          <t>840966</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1665216</t>
+          <t>937122</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>13,24%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3105769</t>
+          <t>3152534</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3069005</t>
+          <t>3120755</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3167849</t>
+          <t>3182975</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>90,9%</t>
+          <t>90,65%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>2821618</t>
+          <t>3036360</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2295084</t>
+          <t>2999915</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3008680</t>
+          <t>3072268</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>78,87%</t>
+          <t>83,52%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>64,15%</t>
+          <t>82,52%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>84,09%</t>
+          <t>84,51%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>5927386</t>
+          <t>6188894</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5288602</t>
+          <t>6140747</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6131127</t>
+          <t>6236903</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>85,24%</t>
+          <t>87,44%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>76,05%</t>
+          <t>86,76%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>88,12%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
